--- a/recruiter_forms/003_talent_acquisition_form--recruiter_forms.xlsx
+++ b/recruiter_forms/003_talent_acquisition_form--recruiter_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1056,8 +1056,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_18,_'label':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 18, 'label': 'Open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_19,_'label':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 19, 'label': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_20,_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 20, 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_21,_'label':_'hr'}</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 21, 'label': 'HR'}</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_22,_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 22, 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_23,_'label':_'recruiter'}</t>
+          <t>recruiter</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 23, 'label': 'Recruiter'}</t>
+          <t>Recruiter</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_24,_'label':_'team_member'}</t>
+          <t>team_member</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 24, 'label': 'Team Member'}</t>
+          <t>Team Member</t>
         </is>
       </c>
     </row>
